--- a/Sina/config/stock_codes.xlsx
+++ b/Sina/config/stock_codes.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11960"/>
+    <workbookView windowHeight="16580"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$438</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$437</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,54 +30,1287 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="437">
   <si>
     <t>stock_code</t>
   </si>
   <si>
+    <t>sh000001</t>
+  </si>
+  <si>
+    <t>sh000012</t>
+  </si>
+  <si>
+    <t>sh600006</t>
+  </si>
+  <si>
+    <t>sh600009</t>
+  </si>
+  <si>
+    <t>sh600027</t>
+  </si>
+  <si>
+    <t>sh600037</t>
+  </si>
+  <si>
+    <t>sh600039</t>
+  </si>
+  <si>
+    <t>sh600053</t>
+  </si>
+  <si>
+    <t>sh600054</t>
+  </si>
+  <si>
+    <t>sh600055</t>
+  </si>
+  <si>
+    <t>sh600058</t>
+  </si>
+  <si>
+    <t>sh600089</t>
+  </si>
+  <si>
+    <t>sh600098</t>
+  </si>
+  <si>
+    <t>sh600119</t>
+  </si>
+  <si>
+    <t>sh600132</t>
+  </si>
+  <si>
+    <t>sh600135</t>
+  </si>
+  <si>
+    <t>sh600143</t>
+  </si>
+  <si>
+    <t>sh600148</t>
+  </si>
+  <si>
+    <t>sh600153</t>
+  </si>
+  <si>
+    <t>sh600157</t>
+  </si>
+  <si>
+    <t>sh600176</t>
+  </si>
+  <si>
+    <t>sh600177</t>
+  </si>
+  <si>
+    <t>sh600185</t>
+  </si>
+  <si>
+    <t>sh600198</t>
+  </si>
+  <si>
+    <t>sh600206</t>
+  </si>
+  <si>
+    <t>sh600212</t>
+  </si>
+  <si>
+    <t>sh600230</t>
+  </si>
+  <si>
+    <t>sh600235</t>
+  </si>
+  <si>
+    <t>sh600268</t>
+  </si>
+  <si>
+    <t>sh600271</t>
+  </si>
+  <si>
+    <t>sh600280</t>
+  </si>
+  <si>
+    <t>sh600283</t>
+  </si>
+  <si>
+    <t>sh600292</t>
+  </si>
+  <si>
+    <t>sh600305</t>
+  </si>
+  <si>
+    <t>sh600336</t>
+  </si>
+  <si>
+    <t>sh600338</t>
+  </si>
+  <si>
+    <t>sh600340</t>
+  </si>
+  <si>
+    <t>sh600392</t>
+  </si>
+  <si>
+    <t>sh600408</t>
+  </si>
+  <si>
+    <t>sh600435</t>
+  </si>
+  <si>
+    <t>sh600477</t>
+  </si>
+  <si>
+    <t>sh600489</t>
+  </si>
+  <si>
+    <t>sh600497</t>
+  </si>
+  <si>
+    <t>sh600507</t>
+  </si>
+  <si>
+    <t>sh600518</t>
+  </si>
+  <si>
+    <t>sh600522</t>
+  </si>
+  <si>
+    <t>sh600523</t>
+  </si>
+  <si>
+    <t>sh600529</t>
+  </si>
+  <si>
+    <t>sh600536</t>
+  </si>
+  <si>
+    <t>sh600546</t>
+  </si>
+  <si>
+    <t>sh600548</t>
+  </si>
+  <si>
+    <t>sh600550</t>
+  </si>
+  <si>
+    <t>sh600558</t>
+  </si>
+  <si>
+    <t>sh600563</t>
+  </si>
+  <si>
+    <t>sh600579</t>
+  </si>
+  <si>
+    <t>sh600584</t>
+  </si>
+  <si>
+    <t>sh600587</t>
+  </si>
+  <si>
+    <t>sh600588</t>
+  </si>
+  <si>
+    <t>sh600616</t>
+  </si>
+  <si>
+    <t>sh600621</t>
+  </si>
+  <si>
+    <t>sh600622</t>
+  </si>
+  <si>
     <t>sh600635</t>
   </si>
   <si>
+    <t>sh600675</t>
+  </si>
+  <si>
+    <t>sh600694</t>
+  </si>
+  <si>
+    <t>sh600702</t>
+  </si>
+  <si>
+    <t>sh600706</t>
+  </si>
+  <si>
+    <t>sh600712</t>
+  </si>
+  <si>
+    <t>sh600724</t>
+  </si>
+  <si>
+    <t>sh600729</t>
+  </si>
+  <si>
+    <t>sh600739</t>
+  </si>
+  <si>
+    <t>sh600748</t>
+  </si>
+  <si>
+    <t>sh600754</t>
+  </si>
+  <si>
+    <t>sh600756</t>
+  </si>
+  <si>
+    <t>sh600757</t>
+  </si>
+  <si>
+    <t>sh600764</t>
+  </si>
+  <si>
+    <t>sh600789</t>
+  </si>
+  <si>
+    <t>sh600797</t>
+  </si>
+  <si>
+    <t>sh600829</t>
+  </si>
+  <si>
+    <t>sh600838</t>
+  </si>
+  <si>
+    <t>sh600871</t>
+  </si>
+  <si>
+    <t>sh600872</t>
+  </si>
+  <si>
+    <t>sh600875</t>
+  </si>
+  <si>
+    <t>sh600895</t>
+  </si>
+  <si>
+    <t>sh600903</t>
+  </si>
+  <si>
+    <t>sh600963</t>
+  </si>
+  <si>
+    <t>sh600976</t>
+  </si>
+  <si>
+    <t>sh600984</t>
+  </si>
+  <si>
+    <t>sh600988</t>
+  </si>
+  <si>
+    <t>sh601000</t>
+  </si>
+  <si>
+    <t>sh601010</t>
+  </si>
+  <si>
+    <t>sh601021</t>
+  </si>
+  <si>
+    <t>sh601061</t>
+  </si>
+  <si>
+    <t>sh601086</t>
+  </si>
+  <si>
+    <t>sh601106</t>
+  </si>
+  <si>
+    <t>sh601108</t>
+  </si>
+  <si>
+    <t>sh601136</t>
+  </si>
+  <si>
+    <t>sh601139</t>
+  </si>
+  <si>
+    <t>sh601155</t>
+  </si>
+  <si>
+    <t>sh601162</t>
+  </si>
+  <si>
+    <t>sh601198</t>
+  </si>
+  <si>
+    <t>sh601216</t>
+  </si>
+  <si>
+    <t>sh601369</t>
+  </si>
+  <si>
+    <t>sh601566</t>
+  </si>
+  <si>
+    <t>sh601608</t>
+  </si>
+  <si>
+    <t>sh601665</t>
+  </si>
+  <si>
+    <t>sh601669</t>
+  </si>
+  <si>
+    <t>sh601702</t>
+  </si>
+  <si>
+    <t>sh601778</t>
+  </si>
+  <si>
+    <t>sh601788</t>
+  </si>
+  <si>
+    <t>sh601877</t>
+  </si>
+  <si>
+    <t>sh601890</t>
+  </si>
+  <si>
+    <t>sh601916</t>
+  </si>
+  <si>
+    <t>sh601933</t>
+  </si>
+  <si>
+    <t>sh601975</t>
+  </si>
+  <si>
+    <t>sh601990</t>
+  </si>
+  <si>
+    <t>sh603002</t>
+  </si>
+  <si>
+    <t>sh603005</t>
+  </si>
+  <si>
+    <t>sh603010</t>
+  </si>
+  <si>
+    <t>sh603025</t>
+  </si>
+  <si>
+    <t>sh603030</t>
+  </si>
+  <si>
+    <t>sh603048</t>
+  </si>
+  <si>
+    <t>sh603055</t>
+  </si>
+  <si>
+    <t>sh603058</t>
+  </si>
+  <si>
+    <t>sh603061</t>
+  </si>
+  <si>
+    <t>sh603063</t>
+  </si>
+  <si>
+    <t>sh603160</t>
+  </si>
+  <si>
+    <t>sh603168</t>
+  </si>
+  <si>
+    <t>sh603188</t>
+  </si>
+  <si>
+    <t>sh603197</t>
+  </si>
+  <si>
+    <t>sh603239</t>
+  </si>
+  <si>
+    <t>sh603259</t>
+  </si>
+  <si>
+    <t>sh603260</t>
+  </si>
+  <si>
+    <t>sh603307</t>
+  </si>
+  <si>
+    <t>sh603316</t>
+  </si>
+  <si>
+    <t>sh603456</t>
+  </si>
+  <si>
+    <t>sh603477</t>
+  </si>
+  <si>
+    <t>sh603601</t>
+  </si>
+  <si>
+    <t>sh603602</t>
+  </si>
+  <si>
+    <t>sh603661</t>
+  </si>
+  <si>
+    <t>sh603667</t>
+  </si>
+  <si>
+    <t>sh603706</t>
+  </si>
+  <si>
+    <t>sh603717</t>
+  </si>
+  <si>
+    <t>sh603790</t>
+  </si>
+  <si>
+    <t>sh603799</t>
+  </si>
+  <si>
+    <t>sh603810</t>
+  </si>
+  <si>
+    <t>sh603816</t>
+  </si>
+  <si>
+    <t>sh603880</t>
+  </si>
+  <si>
+    <t>sh603881</t>
+  </si>
+  <si>
+    <t>sh603885</t>
+  </si>
+  <si>
+    <t>sh603888</t>
+  </si>
+  <si>
+    <t>sh603893</t>
+  </si>
+  <si>
+    <t>sh603949</t>
+  </si>
+  <si>
+    <t>sh603969</t>
+  </si>
+  <si>
+    <t>sh603976</t>
+  </si>
+  <si>
+    <t>sh603989</t>
+  </si>
+  <si>
+    <t>sh605001</t>
+  </si>
+  <si>
+    <t>sh605008</t>
+  </si>
+  <si>
+    <t>sh605117</t>
+  </si>
+  <si>
+    <t>sh605177</t>
+  </si>
+  <si>
+    <t>sh688005</t>
+  </si>
+  <si>
+    <t>sh688017</t>
+  </si>
+  <si>
+    <t>sh688063</t>
+  </si>
+  <si>
+    <t>sh688070</t>
+  </si>
+  <si>
+    <t>sh688099</t>
+  </si>
+  <si>
+    <t>sh688169</t>
+  </si>
+  <si>
+    <t>sh688190</t>
+  </si>
+  <si>
+    <t>sh688231</t>
+  </si>
+  <si>
+    <t>sh688308</t>
+  </si>
+  <si>
+    <t>sh688316</t>
+  </si>
+  <si>
+    <t>sh688400</t>
+  </si>
+  <si>
+    <t>sh688418</t>
+  </si>
+  <si>
+    <t>sh688531</t>
+  </si>
+  <si>
+    <t>sh688556</t>
+  </si>
+  <si>
+    <t>sh688567</t>
+  </si>
+  <si>
+    <t>sh688660</t>
+  </si>
+  <si>
+    <t>sh688721</t>
+  </si>
+  <si>
+    <t>sh689009</t>
+  </si>
+  <si>
+    <t>sh900925</t>
+  </si>
+  <si>
+    <t>sz000009</t>
+  </si>
+  <si>
+    <t>sz000011</t>
+  </si>
+  <si>
+    <t>sz000021</t>
+  </si>
+  <si>
+    <t>sz000025</t>
+  </si>
+  <si>
+    <t>sz000029</t>
+  </si>
+  <si>
+    <t>sz000039</t>
+  </si>
+  <si>
+    <t>sz000049</t>
+  </si>
+  <si>
+    <t>sz000066</t>
+  </si>
+  <si>
+    <t>sz000078</t>
+  </si>
+  <si>
+    <t>sz000156</t>
+  </si>
+  <si>
+    <t>sz000410</t>
+  </si>
+  <si>
+    <t>sz000513</t>
+  </si>
+  <si>
+    <t>sz000519</t>
+  </si>
+  <si>
+    <t>sz000526</t>
+  </si>
+  <si>
+    <t>sz000528</t>
+  </si>
+  <si>
+    <t>sz000529</t>
+  </si>
+  <si>
+    <t>sz000555</t>
+  </si>
+  <si>
+    <t>sz000568</t>
+  </si>
+  <si>
+    <t>sz000596</t>
+  </si>
+  <si>
+    <t>sz000628</t>
+  </si>
+  <si>
+    <t>sz000650</t>
+  </si>
+  <si>
+    <t>sz000661</t>
+  </si>
+  <si>
+    <t>sz000686</t>
+  </si>
+  <si>
+    <t>sz000700</t>
+  </si>
+  <si>
+    <t>sz000723</t>
+  </si>
+  <si>
+    <t>sz000733</t>
+  </si>
+  <si>
+    <t>sz000735</t>
+  </si>
+  <si>
+    <t>sz000738</t>
+  </si>
+  <si>
+    <t>sz000739</t>
+  </si>
+  <si>
+    <t>sz000777</t>
+  </si>
+  <si>
+    <t>sz000782</t>
+  </si>
+  <si>
+    <t>sz000791</t>
+  </si>
+  <si>
+    <t>sz000799</t>
+  </si>
+  <si>
+    <t>sz000810</t>
+  </si>
+  <si>
+    <t>sz000816</t>
+  </si>
+  <si>
+    <t>sz000821</t>
+  </si>
+  <si>
+    <t>sz000831</t>
+  </si>
+  <si>
+    <t>sz000839</t>
+  </si>
+  <si>
+    <t>sz000858</t>
+  </si>
+  <si>
+    <t>sz000868</t>
+  </si>
+  <si>
+    <t>sz000905</t>
+  </si>
+  <si>
+    <t>sz000932</t>
+  </si>
+  <si>
+    <t>sz000963</t>
+  </si>
+  <si>
+    <t>sz000980</t>
+  </si>
+  <si>
+    <t>sz001259</t>
+  </si>
+  <si>
+    <t>sz001299</t>
+  </si>
+  <si>
+    <t>sz001337</t>
+  </si>
+  <si>
+    <t>sz001914</t>
+  </si>
+  <si>
+    <t>sz002006</t>
+  </si>
+  <si>
+    <t>sz002007</t>
+  </si>
+  <si>
+    <t>sz002008</t>
+  </si>
+  <si>
+    <t>sz002014</t>
+  </si>
+  <si>
+    <t>sz002023</t>
+  </si>
+  <si>
+    <t>sz002035</t>
+  </si>
+  <si>
+    <t>sz002037</t>
+  </si>
+  <si>
+    <t>sz002043</t>
+  </si>
+  <si>
+    <t>sz002049</t>
+  </si>
+  <si>
+    <t>sz002067</t>
+  </si>
+  <si>
+    <t>sz002074</t>
+  </si>
+  <si>
+    <t>sz002081</t>
+  </si>
+  <si>
+    <t>sz002086</t>
+  </si>
+  <si>
+    <t>sz002095</t>
+  </si>
+  <si>
+    <t>sz002104</t>
+  </si>
+  <si>
+    <t>sz002112</t>
+  </si>
+  <si>
+    <t>sz002120</t>
+  </si>
+  <si>
+    <t>sz002127</t>
+  </si>
+  <si>
+    <t>sz002128</t>
+  </si>
+  <si>
+    <t>sz002130</t>
+  </si>
+  <si>
+    <t>sz002131</t>
+  </si>
+  <si>
+    <t>sz002153</t>
+  </si>
+  <si>
+    <t>sz002160</t>
+  </si>
+  <si>
+    <t>sz002163</t>
+  </si>
+  <si>
+    <t>sz002167</t>
+  </si>
+  <si>
+    <t>sz002169</t>
+  </si>
+  <si>
+    <t>sz002183</t>
+  </si>
+  <si>
+    <t>sz002185</t>
+  </si>
+  <si>
+    <t>sz002190</t>
+  </si>
+  <si>
+    <t>sz002195</t>
+  </si>
+  <si>
+    <t>sz002204</t>
+  </si>
+  <si>
+    <t>sz002218</t>
+  </si>
+  <si>
+    <t>sz002223</t>
+  </si>
+  <si>
+    <t>sz002233</t>
+  </si>
+  <si>
+    <t>sz002236</t>
+  </si>
+  <si>
+    <t>sz002237</t>
+  </si>
+  <si>
+    <t>sz002239</t>
+  </si>
+  <si>
+    <t>sz002272</t>
+  </si>
+  <si>
+    <t>sz002276</t>
+  </si>
+  <si>
+    <t>sz002291</t>
+  </si>
+  <si>
+    <t>sz002292</t>
+  </si>
+  <si>
+    <t>sz002294</t>
+  </si>
+  <si>
+    <t>sz002306</t>
+  </si>
+  <si>
+    <t>sz002320</t>
+  </si>
+  <si>
+    <t>sz002326</t>
+  </si>
+  <si>
+    <t>sz002328</t>
+  </si>
+  <si>
+    <t>sz002343</t>
+  </si>
+  <si>
+    <t>sz002347</t>
+  </si>
+  <si>
+    <t>sz002353</t>
+  </si>
+  <si>
+    <t>sz002355</t>
+  </si>
+  <si>
+    <t>sz002358</t>
+  </si>
+  <si>
+    <t>sz002369</t>
+  </si>
+  <si>
+    <t>sz002396</t>
+  </si>
+  <si>
+    <t>sz002430</t>
+  </si>
+  <si>
+    <t>sz002439</t>
+  </si>
+  <si>
+    <t>sz002445</t>
+  </si>
+  <si>
+    <t>sz002448</t>
+  </si>
+  <si>
+    <t>sz002458</t>
+  </si>
+  <si>
+    <t>sz002460</t>
+  </si>
+  <si>
+    <t>sz002466</t>
+  </si>
+  <si>
+    <t>sz002475</t>
+  </si>
+  <si>
+    <t>sz002497</t>
+  </si>
+  <si>
+    <t>sz002530</t>
+  </si>
+  <si>
+    <t>sz002545</t>
+  </si>
+  <si>
+    <t>sz002548</t>
+  </si>
+  <si>
+    <t>sz002549</t>
+  </si>
+  <si>
+    <t>sz002555</t>
+  </si>
+  <si>
+    <t>sz002559</t>
+  </si>
+  <si>
+    <t>sz002572</t>
+  </si>
+  <si>
+    <t>sz002573</t>
+  </si>
+  <si>
+    <t>sz002600</t>
+  </si>
+  <si>
+    <t>sz002601</t>
+  </si>
+  <si>
+    <t>sz002602</t>
+  </si>
+  <si>
+    <t>sz002628</t>
+  </si>
+  <si>
+    <t>sz002629</t>
+  </si>
+  <si>
+    <t>sz002646</t>
+  </si>
+  <si>
+    <t>sz002648</t>
+  </si>
+  <si>
+    <t>sz002651</t>
+  </si>
+  <si>
+    <t>sz002654</t>
+  </si>
+  <si>
+    <t>sz002655</t>
+  </si>
+  <si>
+    <t>sz002660</t>
+  </si>
+  <si>
+    <t>sz002669</t>
+  </si>
+  <si>
+    <t>sz002673</t>
+  </si>
+  <si>
+    <t>sz002677</t>
+  </si>
+  <si>
+    <t>sz002745</t>
+  </si>
+  <si>
+    <t>sz002747</t>
+  </si>
+  <si>
+    <t>sz002756</t>
+  </si>
+  <si>
+    <t>sz002795</t>
+  </si>
+  <si>
+    <t>sz002812</t>
+  </si>
+  <si>
+    <t>sz002821</t>
+  </si>
+  <si>
+    <t>sz002843</t>
+  </si>
+  <si>
+    <t>sz002903</t>
+  </si>
+  <si>
+    <t>sz002908</t>
+  </si>
+  <si>
+    <t>sz002909</t>
+  </si>
+  <si>
+    <t>sz002932</t>
+  </si>
+  <si>
+    <t>sz002936</t>
+  </si>
+  <si>
+    <t>sz002940</t>
+  </si>
+  <si>
+    <t>sz002943</t>
+  </si>
+  <si>
+    <t>sz002959</t>
+  </si>
+  <si>
+    <t>sz002965</t>
+  </si>
+  <si>
+    <t>sz002972</t>
+  </si>
+  <si>
+    <t>sz002985</t>
+  </si>
+  <si>
+    <t>sz003001</t>
+  </si>
+  <si>
+    <t>sz003025</t>
+  </si>
+  <si>
+    <t>sz300001</t>
+  </si>
+  <si>
+    <t>sz300008</t>
+  </si>
+  <si>
+    <t>sz300017</t>
+  </si>
+  <si>
+    <t>sz300020</t>
+  </si>
+  <si>
+    <t>sz300024</t>
+  </si>
+  <si>
+    <t>sz300051</t>
+  </si>
+  <si>
+    <t>sz300055</t>
+  </si>
+  <si>
+    <t>sz300056</t>
+  </si>
+  <si>
+    <t>sz300061</t>
+  </si>
+  <si>
+    <t>sz300083</t>
+  </si>
+  <si>
+    <t>sz300084</t>
+  </si>
+  <si>
+    <t>sz300122</t>
+  </si>
+  <si>
+    <t>sz300145</t>
+  </si>
+  <si>
+    <t>sz300146</t>
+  </si>
+  <si>
+    <t>sz300149</t>
+  </si>
+  <si>
+    <t>sz300166</t>
+  </si>
+  <si>
+    <t>sz300175</t>
+  </si>
+  <si>
+    <t>sz300180</t>
+  </si>
+  <si>
+    <t>sz300198</t>
+  </si>
+  <si>
+    <t>sz300212</t>
+  </si>
+  <si>
+    <t>sz300221</t>
+  </si>
+  <si>
     <t>sz300243</t>
   </si>
   <si>
+    <t>sz300271</t>
+  </si>
+  <si>
+    <t>sz300278</t>
+  </si>
+  <si>
+    <t>sz300285</t>
+  </si>
+  <si>
     <t>sz300315</t>
   </si>
   <si>
-    <t>sh688070</t>
-  </si>
-  <si>
-    <t>sh601788</t>
-  </si>
-  <si>
-    <t>sz000519</t>
-  </si>
-  <si>
-    <t>sh603601</t>
+    <t>sz300316</t>
+  </si>
+  <si>
+    <t>sz300322</t>
+  </si>
+  <si>
+    <t>sz300339</t>
+  </si>
+  <si>
+    <t>sz300343</t>
+  </si>
+  <si>
+    <t>sz300346</t>
+  </si>
+  <si>
+    <t>sz300355</t>
+  </si>
+  <si>
+    <t>sz300383</t>
+  </si>
+  <si>
+    <t>sz300397</t>
+  </si>
+  <si>
+    <t>sz300407</t>
+  </si>
+  <si>
+    <t>sz300416</t>
+  </si>
+  <si>
+    <t>sz300424</t>
+  </si>
+  <si>
+    <t>sz300430</t>
   </si>
   <si>
     <t>sz300444</t>
   </si>
   <si>
+    <t>sz300450</t>
+  </si>
+  <si>
+    <t>sz300454</t>
+  </si>
+  <si>
+    <t>sz300458</t>
+  </si>
+  <si>
     <t>sz300461</t>
   </si>
   <si>
-    <t>sz002972</t>
-  </si>
-  <si>
-    <t>sh601162</t>
-  </si>
-  <si>
-    <t>sz000686</t>
-  </si>
-  <si>
-    <t>sz000963</t>
-  </si>
-  <si>
-    <t>sz001259</t>
-  </si>
-  <si>
-    <t>sh603307</t>
+    <t>sz300467</t>
+  </si>
+  <si>
+    <t>sz300469</t>
+  </si>
+  <si>
+    <t>sz300471</t>
+  </si>
+  <si>
+    <t>sz300491</t>
+  </si>
+  <si>
+    <t>sz300496</t>
+  </si>
+  <si>
+    <t>sz300503</t>
+  </si>
+  <si>
+    <t>sz300506</t>
+  </si>
+  <si>
+    <t>sz300525</t>
+  </si>
+  <si>
+    <t>sz300529</t>
+  </si>
+  <si>
+    <t>sz300542</t>
+  </si>
+  <si>
+    <t>sz300564</t>
+  </si>
+  <si>
+    <t>sz300569</t>
+  </si>
+  <si>
+    <t>sz300579</t>
+  </si>
+  <si>
+    <t>sz300596</t>
+  </si>
+  <si>
+    <t>sz300601</t>
+  </si>
+  <si>
+    <t>sz300618</t>
+  </si>
+  <si>
+    <t>sz300624</t>
+  </si>
+  <si>
+    <t>sz300625</t>
+  </si>
+  <si>
+    <t>sz300628</t>
+  </si>
+  <si>
+    <t>sz300636</t>
+  </si>
+  <si>
+    <t>sz300648</t>
+  </si>
+  <si>
+    <t>sz300664</t>
+  </si>
+  <si>
+    <t>sz300671</t>
+  </si>
+  <si>
+    <t>sz300674</t>
+  </si>
+  <si>
+    <t>sz300676</t>
+  </si>
+  <si>
+    <t>sz300677</t>
+  </si>
+  <si>
+    <t>sz300682</t>
+  </si>
+  <si>
+    <t>sz300686</t>
+  </si>
+  <si>
+    <t>sz300693</t>
+  </si>
+  <si>
+    <t>sz300705</t>
+  </si>
+  <si>
+    <t>sz300710</t>
+  </si>
+  <si>
+    <t>sz300711</t>
+  </si>
+  <si>
+    <t>sz300713</t>
+  </si>
+  <si>
+    <t>sz300735</t>
+  </si>
+  <si>
+    <t>sz300741</t>
+  </si>
+  <si>
+    <t>sz300747</t>
+  </si>
+  <si>
+    <t>sz300751</t>
+  </si>
+  <si>
+    <t>sz300767</t>
+  </si>
+  <si>
+    <t>sz300769</t>
+  </si>
+  <si>
+    <t>sz300773</t>
+  </si>
+  <si>
+    <t>sz300796</t>
+  </si>
+  <si>
+    <t>sz300807</t>
+  </si>
+  <si>
+    <t>sz300809</t>
+  </si>
+  <si>
+    <t>sz300829</t>
+  </si>
+  <si>
+    <t>sz300832</t>
+  </si>
+  <si>
+    <t>sz300833</t>
+  </si>
+  <si>
+    <t>sz300836</t>
+  </si>
+  <si>
+    <t>sz300842</t>
+  </si>
+  <si>
+    <t>sz300869</t>
+  </si>
+  <si>
+    <t>sz300943</t>
+  </si>
+  <si>
+    <t>sz300963</t>
+  </si>
+  <si>
+    <t>sz300995</t>
+  </si>
+  <si>
+    <t>sz301107</t>
   </si>
   <si>
     <t>sz301227</t>
@@ -86,1264 +1319,28 @@
     <t>sz301234</t>
   </si>
   <si>
+    <t>sz301251</t>
+  </si>
+  <si>
+    <t>sz301257</t>
+  </si>
+  <si>
+    <t>sz301287</t>
+  </si>
+  <si>
+    <t>sz301359</t>
+  </si>
+  <si>
     <t>sz301388</t>
   </si>
   <si>
-    <t>sh600392</t>
-  </si>
-  <si>
-    <t>sz002965</t>
-  </si>
-  <si>
-    <t>sz000733</t>
-  </si>
-  <si>
-    <t>sz300542</t>
-  </si>
-  <si>
-    <t>sz002195</t>
-  </si>
-  <si>
-    <t>sh600739</t>
-  </si>
-  <si>
-    <t>sz001299</t>
-  </si>
-  <si>
-    <t>sz002548</t>
-  </si>
-  <si>
-    <t>sh688017</t>
-  </si>
-  <si>
-    <t>sz300166</t>
-  </si>
-  <si>
-    <t>sz002628</t>
-  </si>
-  <si>
-    <t>sh688316</t>
-  </si>
-  <si>
-    <t>sz301107</t>
-  </si>
-  <si>
-    <t>sh688099</t>
-  </si>
-  <si>
-    <t>sz002439</t>
-  </si>
-  <si>
-    <t>sh600523</t>
-  </si>
-  <si>
-    <t>sz002677</t>
-  </si>
-  <si>
-    <t>sz300430</t>
-  </si>
-  <si>
-    <t>sz002355</t>
-  </si>
-  <si>
-    <t>sh600838</t>
-  </si>
-  <si>
-    <t>sz002646</t>
-  </si>
-  <si>
-    <t>sz000738</t>
-  </si>
-  <si>
-    <t>sz000777</t>
-  </si>
-  <si>
-    <t>sh688418</t>
-  </si>
-  <si>
-    <t>sh600039</t>
-  </si>
-  <si>
-    <t>sz301251</t>
-  </si>
-  <si>
-    <t>sh603893</t>
-  </si>
-  <si>
-    <t>sz300346</t>
-  </si>
-  <si>
-    <t>sh600621</t>
-  </si>
-  <si>
-    <t>sh603055</t>
-  </si>
-  <si>
-    <t>sh000001</t>
-  </si>
-  <si>
-    <t>sz301359</t>
-  </si>
-  <si>
-    <t>sh600185</t>
-  </si>
-  <si>
-    <t>sz002475</t>
-  </si>
-  <si>
-    <t>sz300671</t>
-  </si>
-  <si>
-    <t>sh603259</t>
-  </si>
-  <si>
-    <t>sh000012</t>
-  </si>
-  <si>
-    <t>sh605117</t>
-  </si>
-  <si>
-    <t>sh605177</t>
-  </si>
-  <si>
-    <t>sh603188</t>
-  </si>
-  <si>
-    <t>sh600230</t>
-  </si>
-  <si>
-    <t>sz002008</t>
-  </si>
-  <si>
-    <t>sz300564</t>
-  </si>
-  <si>
-    <t>sh601702</t>
-  </si>
-  <si>
-    <t>sz003001</t>
-  </si>
-  <si>
-    <t>sz300809</t>
-  </si>
-  <si>
-    <t>sh603477</t>
+    <t>sz301503</t>
+  </si>
+  <si>
+    <t>sz301512</t>
   </si>
   <si>
     <t>sz301525</t>
-  </si>
-  <si>
-    <t>sz002985</t>
-  </si>
-  <si>
-    <t>sz300503</t>
-  </si>
-  <si>
-    <t>sz300842</t>
-  </si>
-  <si>
-    <t>sh688721</t>
-  </si>
-  <si>
-    <t>sz300693</t>
-  </si>
-  <si>
-    <t>sh689009</t>
-  </si>
-  <si>
-    <t>sz003025</t>
-  </si>
-  <si>
-    <t>sz301512</t>
-  </si>
-  <si>
-    <t>sz002006</t>
-  </si>
-  <si>
-    <t>sz002014</t>
-  </si>
-  <si>
-    <t>sh600694</t>
-  </si>
-  <si>
-    <t>sh688556</t>
-  </si>
-  <si>
-    <t>sh688308</t>
-  </si>
-  <si>
-    <t>sh688531</t>
-  </si>
-  <si>
-    <t>sh600518</t>
-  </si>
-  <si>
-    <t>sz300624</t>
-  </si>
-  <si>
-    <t>sh603048</t>
-  </si>
-  <si>
-    <t>sh600292</t>
-  </si>
-  <si>
-    <t>sz002023</t>
-  </si>
-  <si>
-    <t>sz300416</t>
-  </si>
-  <si>
-    <t>sz000868</t>
-  </si>
-  <si>
-    <t>sz300322</t>
-  </si>
-  <si>
-    <t>sh600579</t>
-  </si>
-  <si>
-    <t>sz300713</t>
-  </si>
-  <si>
-    <t>sz301503</t>
-  </si>
-  <si>
-    <t>sh600212</t>
-  </si>
-  <si>
-    <t>sz300491</t>
-  </si>
-  <si>
-    <t>sz002037</t>
-  </si>
-  <si>
-    <t>sz002602</t>
-  </si>
-  <si>
-    <t>sh601061</t>
-  </si>
-  <si>
-    <t>sz300995</t>
-  </si>
-  <si>
-    <t>sz300355</t>
-  </si>
-  <si>
-    <t>sz001337</t>
-  </si>
-  <si>
-    <t>sh600895</t>
-  </si>
-  <si>
-    <t>sh603168</t>
-  </si>
-  <si>
-    <t>sz300056</t>
-  </si>
-  <si>
-    <t>sz002756</t>
-  </si>
-  <si>
-    <t>sz002651</t>
-  </si>
-  <si>
-    <t>sz301257</t>
-  </si>
-  <si>
-    <t>sh600054</t>
-  </si>
-  <si>
-    <t>sz300625</t>
-  </si>
-  <si>
-    <t>sh600706</t>
-  </si>
-  <si>
-    <t>sh603061</t>
-  </si>
-  <si>
-    <t>sh601136</t>
-  </si>
-  <si>
-    <t>sh600616</t>
-  </si>
-  <si>
-    <t>sz000528</t>
-  </si>
-  <si>
-    <t>sh688231</t>
-  </si>
-  <si>
-    <t>sh688400</t>
-  </si>
-  <si>
-    <t>sz300383</t>
-  </si>
-  <si>
-    <t>sz300145</t>
-  </si>
-  <si>
-    <t>sh688190</t>
-  </si>
-  <si>
-    <t>sz002204</t>
-  </si>
-  <si>
-    <t>sz300618</t>
-  </si>
-  <si>
-    <t>sh601665</t>
-  </si>
-  <si>
-    <t>sz300767</t>
-  </si>
-  <si>
-    <t>sh688660</t>
-  </si>
-  <si>
-    <t>sz300943</t>
-  </si>
-  <si>
-    <t>sh603160</t>
-  </si>
-  <si>
-    <t>sz300458</t>
-  </si>
-  <si>
-    <t>sz300829</t>
-  </si>
-  <si>
-    <t>sh600143</t>
-  </si>
-  <si>
-    <t>sh516160</t>
-  </si>
-  <si>
-    <t>sz300751</t>
-  </si>
-  <si>
-    <t>sh603799</t>
-  </si>
-  <si>
-    <t>sh688567</t>
-  </si>
-  <si>
-    <t>sz002074</t>
-  </si>
-  <si>
-    <t>sz002812</t>
-  </si>
-  <si>
-    <t>sz300198</t>
-  </si>
-  <si>
-    <t>sh688005</t>
-  </si>
-  <si>
-    <t>sh688063</t>
-  </si>
-  <si>
-    <t>sz002127</t>
-  </si>
-  <si>
-    <t>sz002745</t>
-  </si>
-  <si>
-    <t>sh600336</t>
-  </si>
-  <si>
-    <t>sh600529</t>
-  </si>
-  <si>
-    <t>sh600009</t>
-  </si>
-  <si>
-    <t>sz300769</t>
-  </si>
-  <si>
-    <t>sz300001</t>
-  </si>
-  <si>
-    <t>sz002747</t>
-  </si>
-  <si>
-    <t>sz000066</t>
-  </si>
-  <si>
-    <t>sh600536</t>
-  </si>
-  <si>
-    <t>sh603002</t>
-  </si>
-  <si>
-    <t>sh600006</t>
-  </si>
-  <si>
-    <t>sh603239</t>
-  </si>
-  <si>
-    <t>sz002112</t>
-  </si>
-  <si>
-    <t>sh605008</t>
-  </si>
-  <si>
-    <t>sz002272</t>
-  </si>
-  <si>
-    <t>sh600563</t>
-  </si>
-  <si>
-    <t>sz002007</t>
-  </si>
-  <si>
-    <t>sh688169</t>
-  </si>
-  <si>
-    <t>sz300869</t>
-  </si>
-  <si>
-    <t>sh600497</t>
-  </si>
-  <si>
-    <t>sz300836</t>
-  </si>
-  <si>
-    <t>sz300529</t>
-  </si>
-  <si>
-    <t>sz002128</t>
-  </si>
-  <si>
-    <t>sz000831</t>
-  </si>
-  <si>
-    <t>sz300175</t>
-  </si>
-  <si>
-    <t>sz002239</t>
-  </si>
-  <si>
-    <t>sz300146</t>
-  </si>
-  <si>
-    <t>sh603881</t>
-  </si>
-  <si>
-    <t>sz300467</t>
-  </si>
-  <si>
-    <t>sz300212</t>
-  </si>
-  <si>
-    <t>sz300454</t>
-  </si>
-  <si>
-    <t>sz300083</t>
-  </si>
-  <si>
-    <t>sz002903</t>
-  </si>
-  <si>
-    <t>sz000980</t>
-  </si>
-  <si>
-    <t>sz300424</t>
-  </si>
-  <si>
-    <t>sh603316</t>
-  </si>
-  <si>
-    <t>sh603976</t>
-  </si>
-  <si>
-    <t>sz300674</t>
-  </si>
-  <si>
-    <t>sz002655</t>
-  </si>
-  <si>
-    <t>sh600053</t>
-  </si>
-  <si>
-    <t>sh601010</t>
-  </si>
-  <si>
-    <t>sh600963</t>
-  </si>
-  <si>
-    <t>sh601086</t>
-  </si>
-  <si>
-    <t>sz000782</t>
-  </si>
-  <si>
-    <t>sz300278</t>
-  </si>
-  <si>
-    <t>sh600550</t>
-  </si>
-  <si>
-    <t>sh600027</t>
-  </si>
-  <si>
-    <t>sz000791</t>
-  </si>
-  <si>
-    <t>sh601216</t>
-  </si>
-  <si>
-    <t>sz002049</t>
-  </si>
-  <si>
-    <t>sz002185</t>
-  </si>
-  <si>
-    <t>sz000009</t>
-  </si>
-  <si>
-    <t>sz000650</t>
-  </si>
-  <si>
-    <t>sh601669</t>
-  </si>
-  <si>
-    <t>sz002131</t>
-  </si>
-  <si>
-    <t>sh600268</t>
-  </si>
-  <si>
-    <t>sh600305</t>
-  </si>
-  <si>
-    <t>sz300710</t>
-  </si>
-  <si>
-    <t>sz002160</t>
-  </si>
-  <si>
-    <t>sz002183</t>
-  </si>
-  <si>
-    <t>sh600408</t>
-  </si>
-  <si>
-    <t>sh600757</t>
-  </si>
-  <si>
-    <t>sh600157</t>
-  </si>
-  <si>
-    <t>sz000723</t>
-  </si>
-  <si>
-    <t>sh601778</t>
-  </si>
-  <si>
-    <t>sh600477</t>
-  </si>
-  <si>
-    <t>sz002320</t>
-  </si>
-  <si>
-    <t>sz002169</t>
-  </si>
-  <si>
-    <t>sh605001</t>
-  </si>
-  <si>
-    <t>sz300450</t>
-  </si>
-  <si>
-    <t>sz300833</t>
-  </si>
-  <si>
-    <t>sz002660</t>
-  </si>
-  <si>
-    <t>sh603949</t>
-  </si>
-  <si>
-    <t>sz300832</t>
-  </si>
-  <si>
-    <t>sz002466</t>
-  </si>
-  <si>
-    <t>sh603706</t>
-  </si>
-  <si>
-    <t>sz000049</t>
-  </si>
-  <si>
-    <t>sh600198</t>
-  </si>
-  <si>
-    <t>sh600764</t>
-  </si>
-  <si>
-    <t>sh600148</t>
-  </si>
-  <si>
-    <t>sh601990</t>
-  </si>
-  <si>
-    <t>sz300735</t>
-  </si>
-  <si>
-    <t>sh603197</t>
-  </si>
-  <si>
-    <t>sh600724</t>
-  </si>
-  <si>
-    <t>sz000661</t>
-  </si>
-  <si>
-    <t>sh600675</t>
-  </si>
-  <si>
-    <t>sz300601</t>
-  </si>
-  <si>
-    <t>sz300122</t>
-  </si>
-  <si>
-    <t>sz002237</t>
-  </si>
-  <si>
-    <t>sz300773</t>
-  </si>
-  <si>
-    <t>sz300496</t>
-  </si>
-  <si>
-    <t>sz300579</t>
-  </si>
-  <si>
-    <t>sz002163</t>
-  </si>
-  <si>
-    <t>sz300636</t>
-  </si>
-  <si>
-    <t>sz300051</t>
-  </si>
-  <si>
-    <t>sz002559</t>
-  </si>
-  <si>
-    <t>sz300024</t>
-  </si>
-  <si>
-    <t>sh603885</t>
-  </si>
-  <si>
-    <t>sh600875</t>
-  </si>
-  <si>
-    <t>sz000700</t>
-  </si>
-  <si>
-    <t>sh603005</t>
-  </si>
-  <si>
-    <t>sz002396</t>
-  </si>
-  <si>
-    <t>sz002369</t>
-  </si>
-  <si>
-    <t>sh600206</t>
-  </si>
-  <si>
-    <t>sz000810</t>
-  </si>
-  <si>
-    <t>sz300686</t>
-  </si>
-  <si>
-    <t>sz002943</t>
-  </si>
-  <si>
-    <t>sh603880</t>
-  </si>
-  <si>
-    <t>sh603989</t>
-  </si>
-  <si>
-    <t>sz300271</t>
-  </si>
-  <si>
-    <t>sz300469</t>
-  </si>
-  <si>
-    <t>sz300807</t>
-  </si>
-  <si>
-    <t>sz000156</t>
-  </si>
-  <si>
-    <t>sz002932</t>
-  </si>
-  <si>
-    <t>sz002530</t>
-  </si>
-  <si>
-    <t>sz300648</t>
-  </si>
-  <si>
-    <t>sz002326</t>
-  </si>
-  <si>
-    <t>sh603456</t>
-  </si>
-  <si>
-    <t>sz000078</t>
-  </si>
-  <si>
-    <t>sz000799</t>
-  </si>
-  <si>
-    <t>sz002940</t>
-  </si>
-  <si>
-    <t>sh600789</t>
-  </si>
-  <si>
-    <t>sz002430</t>
-  </si>
-  <si>
-    <t>sz300747</t>
-  </si>
-  <si>
-    <t>sz300569</t>
-  </si>
-  <si>
-    <t>sh600435</t>
-  </si>
-  <si>
-    <t>sh600098</t>
-  </si>
-  <si>
-    <t>sz300149</t>
-  </si>
-  <si>
-    <t>sz002497</t>
-  </si>
-  <si>
-    <t>sz300407</t>
-  </si>
-  <si>
-    <t>sh603888</t>
-  </si>
-  <si>
-    <t>sz300339</t>
-  </si>
-  <si>
-    <t>sz300343</t>
-  </si>
-  <si>
-    <t>sz000410</t>
-  </si>
-  <si>
-    <t>sh600588</t>
-  </si>
-  <si>
-    <t>sz002795</t>
-  </si>
-  <si>
-    <t>sz300055</t>
-  </si>
-  <si>
-    <t>sh600702</t>
-  </si>
-  <si>
-    <t>sz002600</t>
-  </si>
-  <si>
-    <t>sh600548</t>
-  </si>
-  <si>
-    <t>sz002669</t>
-  </si>
-  <si>
-    <t>sh603260</t>
-  </si>
-  <si>
-    <t>sz002294</t>
-  </si>
-  <si>
-    <t>sh600748</t>
-  </si>
-  <si>
-    <t>sz002343</t>
-  </si>
-  <si>
-    <t>sz300221</t>
-  </si>
-  <si>
-    <t>sh600489</t>
-  </si>
-  <si>
-    <t>sh600338</t>
-  </si>
-  <si>
-    <t>sh603063</t>
-  </si>
-  <si>
-    <t>sz300020</t>
-  </si>
-  <si>
-    <t>sh603717</t>
-  </si>
-  <si>
-    <t>sz002458</t>
-  </si>
-  <si>
-    <t>sz300796</t>
-  </si>
-  <si>
-    <t>sz002959</t>
-  </si>
-  <si>
-    <t>sz000029</t>
-  </si>
-  <si>
-    <t>sz000011</t>
-  </si>
-  <si>
-    <t>sz000021</t>
-  </si>
-  <si>
-    <t>sh601916</t>
-  </si>
-  <si>
-    <t>sh600988</t>
-  </si>
-  <si>
-    <t>sh600903</t>
-  </si>
-  <si>
-    <t>sz000529</t>
-  </si>
-  <si>
-    <t>sh601975</t>
-  </si>
-  <si>
-    <t>sz000513</t>
-  </si>
-  <si>
-    <t>sz002909</t>
-  </si>
-  <si>
-    <t>sh601155</t>
-  </si>
-  <si>
-    <t>sz300471</t>
-  </si>
-  <si>
-    <t>sh600283</t>
-  </si>
-  <si>
-    <t>sh601608</t>
-  </si>
-  <si>
-    <t>sz002190</t>
-  </si>
-  <si>
-    <t>sh600177</t>
-  </si>
-  <si>
-    <t>sz300741</t>
-  </si>
-  <si>
-    <t>sz002292</t>
-  </si>
-  <si>
-    <t>sh600235</t>
-  </si>
-  <si>
-    <t>sh600089</t>
-  </si>
-  <si>
-    <t>sz300711</t>
-  </si>
-  <si>
-    <t>sh603602</t>
-  </si>
-  <si>
-    <t>sh600280</t>
-  </si>
-  <si>
-    <t>sh600622</t>
-  </si>
-  <si>
-    <t>sh603010</t>
-  </si>
-  <si>
-    <t>sz300506</t>
-  </si>
-  <si>
-    <t>sz002236</t>
-  </si>
-  <si>
-    <t>sz300525</t>
-  </si>
-  <si>
-    <t>sz002908</t>
-  </si>
-  <si>
-    <t>sz300180</t>
-  </si>
-  <si>
-    <t>sh600754</t>
-  </si>
-  <si>
-    <t>sz002821</t>
-  </si>
-  <si>
-    <t>sh600271</t>
-  </si>
-  <si>
-    <t>sh600984</t>
-  </si>
-  <si>
-    <t>sh601021</t>
-  </si>
-  <si>
-    <t>sh600584</t>
-  </si>
-  <si>
-    <t>sh601139</t>
-  </si>
-  <si>
-    <t>sz002629</t>
-  </si>
-  <si>
-    <t>sh603790</t>
-  </si>
-  <si>
-    <t>sz002936</t>
-  </si>
-  <si>
-    <t>sh603810</t>
-  </si>
-  <si>
-    <t>sz000735</t>
-  </si>
-  <si>
-    <t>sz300017</t>
-  </si>
-  <si>
-    <t>sz000025</t>
-  </si>
-  <si>
-    <t>sz300664</t>
-  </si>
-  <si>
-    <t>sh600340</t>
-  </si>
-  <si>
-    <t>sh600037</t>
-  </si>
-  <si>
-    <t>sz000932</t>
-  </si>
-  <si>
-    <t>sh603058</t>
-  </si>
-  <si>
-    <t>sh600729</t>
-  </si>
-  <si>
-    <t>sz300676</t>
-  </si>
-  <si>
-    <t>sh601108</t>
-  </si>
-  <si>
-    <t>sh601933</t>
-  </si>
-  <si>
-    <t>sh603661</t>
-  </si>
-  <si>
-    <t>sh603969</t>
-  </si>
-  <si>
-    <t>sh600135</t>
-  </si>
-  <si>
-    <t>sz000839</t>
-  </si>
-  <si>
-    <t>sz002843</t>
-  </si>
-  <si>
-    <t>sz002545</t>
-  </si>
-  <si>
-    <t>sz002460</t>
-  </si>
-  <si>
-    <t>sz002218</t>
-  </si>
-  <si>
-    <t>sz002347</t>
-  </si>
-  <si>
-    <t>sz002549</t>
-  </si>
-  <si>
-    <t>sh601369</t>
-  </si>
-  <si>
-    <t>sz300285</t>
-  </si>
-  <si>
-    <t>sz002167</t>
-  </si>
-  <si>
-    <t>sz300008</t>
-  </si>
-  <si>
-    <t>sz300397</t>
-  </si>
-  <si>
-    <t>sz300682</t>
-  </si>
-  <si>
-    <t>sh600871</t>
-  </si>
-  <si>
-    <t>sz000628</t>
-  </si>
-  <si>
-    <t>sz000526</t>
-  </si>
-  <si>
-    <t>sh603667</t>
-  </si>
-  <si>
-    <t>sh603025</t>
-  </si>
-  <si>
-    <t>sz002673</t>
-  </si>
-  <si>
-    <t>sh601198</t>
-  </si>
-  <si>
-    <t>sz002291</t>
-  </si>
-  <si>
-    <t>sz000555</t>
-  </si>
-  <si>
-    <t>sh600153</t>
-  </si>
-  <si>
-    <t>sh600058</t>
-  </si>
-  <si>
-    <t>sz002654</t>
-  </si>
-  <si>
-    <t>sh600119</t>
-  </si>
-  <si>
-    <t>sz002067</t>
-  </si>
-  <si>
-    <t>sz002358</t>
-  </si>
-  <si>
-    <t>sz002276</t>
-  </si>
-  <si>
-    <t>sz002043</t>
-  </si>
-  <si>
-    <t>sz002445</t>
-  </si>
-  <si>
-    <t>sz002081</t>
-  </si>
-  <si>
-    <t>sh600797</t>
-  </si>
-  <si>
-    <t>sz002328</t>
-  </si>
-  <si>
-    <t>sz002223</t>
-  </si>
-  <si>
-    <t>sz002601</t>
-  </si>
-  <si>
-    <t>sz002573</t>
-  </si>
-  <si>
-    <t>sz000816</t>
-  </si>
-  <si>
-    <t>sz002104</t>
-  </si>
-  <si>
-    <t>sh600558</t>
-  </si>
-  <si>
-    <t>sh601566</t>
-  </si>
-  <si>
-    <t>sh601106</t>
-  </si>
-  <si>
-    <t>sz002095</t>
-  </si>
-  <si>
-    <t>sz002130</t>
-  </si>
-  <si>
-    <t>sz001914</t>
-  </si>
-  <si>
-    <t>sz002306</t>
-  </si>
-  <si>
-    <t>sh600756</t>
-  </si>
-  <si>
-    <t>sh600176</t>
-  </si>
-  <si>
-    <t>sz300061</t>
-  </si>
-  <si>
-    <t>sh600829</t>
-  </si>
-  <si>
-    <t>sz002448</t>
-  </si>
-  <si>
-    <t>sh601000</t>
-  </si>
-  <si>
-    <t>sh600055</t>
-  </si>
-  <si>
-    <t>sz300084</t>
-  </si>
-  <si>
-    <t>sz002353</t>
-  </si>
-  <si>
-    <t>sz002086</t>
-  </si>
-  <si>
-    <t>sh601890</t>
-  </si>
-  <si>
-    <t>sz000039</t>
-  </si>
-  <si>
-    <t>sh603030</t>
-  </si>
-  <si>
-    <t>sz000905</t>
-  </si>
-  <si>
-    <t>sz002153</t>
-  </si>
-  <si>
-    <t>sh600712</t>
-  </si>
-  <si>
-    <t>sz301287</t>
-  </si>
-  <si>
-    <t>sz300963</t>
-  </si>
-  <si>
-    <t>sz300316</t>
-  </si>
-  <si>
-    <t>sz002572</t>
-  </si>
-  <si>
-    <t>sz300677</t>
-  </si>
-  <si>
-    <t>sz000596</t>
-  </si>
-  <si>
-    <t>sh603816</t>
-  </si>
-  <si>
-    <t>sz000568</t>
-  </si>
-  <si>
-    <t>sh600546</t>
-  </si>
-  <si>
-    <t>sz300596</t>
-  </si>
-  <si>
-    <t>sz002555</t>
-  </si>
-  <si>
-    <t>sh600507</t>
-  </si>
-  <si>
-    <t>sh600132</t>
-  </si>
-  <si>
-    <t>sz002648</t>
-  </si>
-  <si>
-    <t>sz002035</t>
-  </si>
-  <si>
-    <t>sz000858</t>
-  </si>
-  <si>
-    <t>sz300628</t>
-  </si>
-  <si>
-    <t>sz002120</t>
-  </si>
-  <si>
-    <t>sh600872</t>
-  </si>
-  <si>
-    <t>sz002233</t>
-  </si>
-  <si>
-    <t>sz300705</t>
-  </si>
-  <si>
-    <t>sh600976</t>
-  </si>
-  <si>
-    <t>sh601877</t>
-  </si>
-  <si>
-    <t>sh600522</t>
-  </si>
-  <si>
-    <t>sz000821</t>
-  </si>
-  <si>
-    <t>sz000739</t>
-  </si>
-  <si>
-    <t>sh600587</t>
-  </si>
-  <si>
-    <t>sh900925</t>
   </si>
 </sst>
 </file>
@@ -2026,13 +2023,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2318,7 +2308,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:A438"/>
+  <dimension ref="A1:A437"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="9.81730769230769" style="1"/>
@@ -2400,7 +2390,7 @@
       </c>
     </row>
     <row r="16" hidden="1" spans="1:1">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2545,7 +2535,7 @@
       </c>
     </row>
     <row r="45" hidden="1" spans="1:1">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="2" t="s">
         <v>44</v>
       </c>
     </row>
@@ -2555,7 +2545,7 @@
       </c>
     </row>
     <row r="47" hidden="1" spans="1:1">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="2" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2575,7 +2565,7 @@
       </c>
     </row>
     <row r="51" hidden="1" spans="1:1">
-      <c r="A51" s="1" t="s">
+      <c r="A51" s="2" t="s">
         <v>50</v>
       </c>
     </row>
@@ -2610,7 +2600,7 @@
       </c>
     </row>
     <row r="58" hidden="1" spans="1:1">
-      <c r="A58" s="1" t="s">
+      <c r="A58" s="2" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2730,7 +2720,7 @@
       </c>
     </row>
     <row r="82" hidden="1" spans="1:1">
-      <c r="A82" s="1" t="s">
+      <c r="A82" s="2" t="s">
         <v>81</v>
       </c>
     </row>
@@ -2755,7 +2745,7 @@
       </c>
     </row>
     <row r="87" hidden="1" spans="1:1">
-      <c r="A87" s="1" t="s">
+      <c r="A87" s="2" t="s">
         <v>86</v>
       </c>
     </row>
@@ -2875,7 +2865,7 @@
       </c>
     </row>
     <row r="111" hidden="1" spans="1:1">
-      <c r="A111" s="1" t="s">
+      <c r="A111" s="2" t="s">
         <v>110</v>
       </c>
     </row>
@@ -3055,7 +3045,7 @@
       </c>
     </row>
     <row r="147" hidden="1" spans="1:1">
-      <c r="A147" s="1" t="s">
+      <c r="A147" s="2" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3215,7 +3205,7 @@
       </c>
     </row>
     <row r="179" hidden="1" spans="1:1">
-      <c r="A179" s="1" t="s">
+      <c r="A179" s="2" t="s">
         <v>178</v>
       </c>
     </row>
@@ -3305,12 +3295,12 @@
       </c>
     </row>
     <row r="197" hidden="1" spans="1:1">
-      <c r="A197" s="1" t="s">
+      <c r="A197" s="2" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="198" hidden="1" spans="1:1">
-      <c r="A198" s="1" t="s">
+      <c r="A198" s="2" t="s">
         <v>197</v>
       </c>
     </row>
@@ -3360,7 +3350,7 @@
       </c>
     </row>
     <row r="208" hidden="1" spans="1:1">
-      <c r="A208" s="1" t="s">
+      <c r="A208" s="2" t="s">
         <v>207</v>
       </c>
     </row>
@@ -3395,7 +3385,7 @@
       </c>
     </row>
     <row r="215" hidden="1" spans="1:1">
-      <c r="A215" s="1" t="s">
+      <c r="A215" s="2" t="s">
         <v>214</v>
       </c>
     </row>
@@ -3410,7 +3400,7 @@
       </c>
     </row>
     <row r="218" hidden="1" spans="1:1">
-      <c r="A218" s="1" t="s">
+      <c r="A218" s="2" t="s">
         <v>217</v>
       </c>
     </row>
@@ -3485,7 +3475,7 @@
       </c>
     </row>
     <row r="233" hidden="1" spans="1:1">
-      <c r="A233" s="1" t="s">
+      <c r="A233" s="2" t="s">
         <v>232</v>
       </c>
     </row>
@@ -3540,7 +3530,7 @@
       </c>
     </row>
     <row r="244" hidden="1" spans="1:1">
-      <c r="A244" s="1" t="s">
+      <c r="A244" s="2" t="s">
         <v>243</v>
       </c>
     </row>
@@ -3625,7 +3615,7 @@
       </c>
     </row>
     <row r="261" hidden="1" spans="1:1">
-      <c r="A261" s="1" t="s">
+      <c r="A261" s="2" t="s">
         <v>260</v>
       </c>
     </row>
@@ -3790,7 +3780,7 @@
       </c>
     </row>
     <row r="294" hidden="1" spans="1:1">
-      <c r="A294" s="1" t="s">
+      <c r="A294" s="2" t="s">
         <v>293</v>
       </c>
     </row>
@@ -3800,7 +3790,7 @@
       </c>
     </row>
     <row r="296" hidden="1" spans="1:1">
-      <c r="A296" s="1" t="s">
+      <c r="A296" s="2" t="s">
         <v>295</v>
       </c>
     </row>
@@ -3840,7 +3830,7 @@
       </c>
     </row>
     <row r="304" hidden="1" spans="1:1">
-      <c r="A304" s="1" t="s">
+      <c r="A304" s="2" t="s">
         <v>303</v>
       </c>
     </row>
@@ -4110,7 +4100,7 @@
       </c>
     </row>
     <row r="358" hidden="1" spans="1:1">
-      <c r="A358" s="1" t="s">
+      <c r="A358" s="2" t="s">
         <v>357</v>
       </c>
     </row>
@@ -4260,7 +4250,7 @@
       </c>
     </row>
     <row r="388" hidden="1" spans="1:1">
-      <c r="A388" s="1" t="s">
+      <c r="A388" s="2" t="s">
         <v>387</v>
       </c>
     </row>
@@ -4285,7 +4275,7 @@
       </c>
     </row>
     <row r="393" hidden="1" spans="1:1">
-      <c r="A393" s="1" t="s">
+      <c r="A393" s="2" t="s">
         <v>392</v>
       </c>
     </row>
@@ -4320,7 +4310,7 @@
       </c>
     </row>
     <row r="400" hidden="1" spans="1:1">
-      <c r="A400" s="1" t="s">
+      <c r="A400" s="2" t="s">
         <v>399</v>
       </c>
     </row>
@@ -4340,7 +4330,7 @@
       </c>
     </row>
     <row r="404" hidden="1" spans="1:1">
-      <c r="A404" s="1" t="s">
+      <c r="A404" s="2" t="s">
         <v>403</v>
       </c>
     </row>
@@ -4385,142 +4375,141 @@
       </c>
     </row>
     <row r="413" hidden="1" spans="1:1">
-      <c r="A413" s="2" t="s">
+      <c r="A413" s="1" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="414" hidden="1" spans="1:1">
-      <c r="A414" s="2" t="s">
+      <c r="A414" s="1" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="415" hidden="1" spans="1:1">
-      <c r="A415" s="2" t="s">
+      <c r="A415" s="1" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="416" hidden="1" spans="1:1">
-      <c r="A416" s="2" t="s">
+      <c r="A416" s="1" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="417" hidden="1" spans="1:1">
-      <c r="A417" s="2" t="s">
+      <c r="A417" s="1" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="418" hidden="1" spans="1:1">
-      <c r="A418" s="2" t="s">
+      <c r="A418" s="1" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="419" hidden="1" spans="1:1">
-      <c r="A419" s="2" t="s">
+      <c r="A419" s="1" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="420" hidden="1" spans="1:1">
-      <c r="A420" s="2" t="s">
+      <c r="A420" s="1" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="421" hidden="1" spans="1:1">
-      <c r="A421" s="2" t="s">
+      <c r="A421" s="1" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="422" hidden="1" spans="1:1">
-      <c r="A422" s="2" t="s">
+      <c r="A422" s="1" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="423" hidden="1" spans="1:1">
-      <c r="A423" s="2" t="s">
+      <c r="A423" s="1" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="424" hidden="1" spans="1:1">
-      <c r="A424" s="2" t="s">
+      <c r="A424" s="1" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="425" hidden="1" spans="1:1">
-      <c r="A425" s="2" t="s">
+      <c r="A425" s="1" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="426" hidden="1" spans="1:1">
-      <c r="A426" s="2" t="s">
+      <c r="A426" s="1" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="427" hidden="1" spans="1:1">
-      <c r="A427" s="2" t="s">
+      <c r="A427" s="1" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="428" hidden="1" spans="1:1">
-      <c r="A428" s="2" t="s">
+      <c r="A428" s="1" t="s">
         <v>427</v>
       </c>
     </row>
     <row r="429" hidden="1" spans="1:1">
-      <c r="A429" s="2" t="s">
+      <c r="A429" s="1" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="430" hidden="1" spans="1:1">
-      <c r="A430" s="2" t="s">
+      <c r="A430" s="1" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="431" hidden="1" spans="1:1">
-      <c r="A431" s="2" t="s">
+      <c r="A431" s="1" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="432" hidden="1" spans="1:1">
-      <c r="A432" s="2" t="s">
+      <c r="A432" s="1" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="433" hidden="1" spans="1:1">
-      <c r="A433" s="2" t="s">
+      <c r="A433" s="1" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="434" hidden="1" spans="1:1">
-      <c r="A434" s="2" t="s">
+      <c r="A434" s="1" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="435" hidden="1" spans="1:1">
-      <c r="A435" s="2" t="s">
+      <c r="A435" s="1" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="436" hidden="1" spans="1:1">
-      <c r="A436" s="2" t="s">
+      <c r="A436" s="1" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="437" hidden="1" spans="1:1">
-      <c r="A437" s="2" t="s">
+      <c r="A437" s="1" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="438" hidden="1" spans="1:1">
-      <c r="A438" s="2" t="s">
-        <v>437</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:A438" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:A437" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="0">
-      <filters>
-        <filter val="sh601028"/>
-      </filters>
+      <customFilters>
+        <customFilter operator="equal" val="*sh5*"/>
+        <customFilter operator="equal" val="*sh399*"/>
+      </customFilters>
     </filterColumn>
+    <sortState ref="A2:A437">
+      <sortCondition ref="A2"/>
+    </sortState>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
